--- a/Informe/diccionario_datos_ALDIMI.xlsx
+++ b/Informe/diccionario_datos_ALDIMI.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset_semanal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset_completo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pacientes_sintetico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo_productos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +140,20 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C8"/>
+  <dimension ref="B2:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -570,6 +585,18 @@
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Dataset sintético de 600 pacientes generado a partir de las fichas de ingreso/reingreso reales de ALDIMI (anonimizado). Insumo del clasificador de riesgo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>catalogo_productos</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Catálogo maestro: nombre visible, presentación, unidad de medida estándar y categoría general por código de artículo.</t>
         </is>
       </c>
     </row>
@@ -584,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F16"/>
+  <dimension ref="B2:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -932,6 +959,141 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>nombre_producto</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Texto libre (602 nombres reales)</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Nombre visible del producto (ej. "Arverja partida 500 gr"). El código queda solo como apoyo de búsqueda</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>presentacion</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>500 gr, 1 kg, 3 lt, 25 und, lata…</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Presentación extraída del kardex original</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>unidad_medida</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>kg, litro, lata, caja, paquete, unidad</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Unidad de medida estándar según el tipo de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>categoria_general</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Avícolas, Menestras, Lácteos, Cereales y farináceos, Conservas, Abarrotes, Bebidas e infusiones, Snacks y dulces, Cárnicos y pescados, Limpieza e higiene, Otros</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Categoría general de negocio (agrupa las 25 categorías específicas en 11 grupos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>es_producto</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Booleana</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>True / False</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>True = producto real con nombre y unidad (se muestra en la app). False = registro técnico o sintético (solo para entrenar modelos)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -943,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F18"/>
+  <dimension ref="B2:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -1342,6 +1504,141 @@
       <c r="F18" s="8" t="inlineStr">
         <is>
           <t>Hoja/almacén de origen del registro en el kardex</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>nombre_producto</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Texto libre (602 nombres reales)</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Nombre visible del producto (ej. "Arverja partida 500 gr"). El código queda solo como apoyo de búsqueda</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>presentacion</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>500 gr, 1 kg, 3 lt, 25 und, lata…</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Presentación extraída del kardex original</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>unidad_medida</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>kg, litro, lata, caja, paquete, unidad</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Unidad de medida estándar según el tipo de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>categoria_general</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Avícolas, Menestras, Lácteos, Cereales y farináceos, Conservas, Abarrotes, Bebidas e infusiones, Snacks y dulces, Cárnicos y pescados, Limpieza e higiene, Otros</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Categoría general de negocio (agrupa las 25 categorías específicas en 11 grupos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>es_producto</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Booleana</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>True / False</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>True = producto real con nombre y unidad (se muestra en la app). False = registro técnico o sintético (solo para entrenar modelos)</t>
         </is>
       </c>
     </row>
@@ -2058,4 +2355,283 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>catalogo_productos.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Catálogo maestro de 1,678 códigos (602 productos reales con nombre y unidad; el resto son registros técnicos/sintéticos usados solo para entrenar). Generado por scripts/build_catalogo.py desde el kardex "ALMAcen upc.xlsx".</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Rango / Valores</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>% Nulos</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>codigo_articulo</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>0001ME … SINT0999 (1678 valores)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Código interno: identifica el registro en la base; en la app aparece solo como apoyo de búsqueda</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>nombre_producto</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Texto libre</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Nombre visible del producto para el usuario operativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>presentacion</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>500 gr, 1 kg, 3 lt, 25 und, lata…</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Presentación extraída del nombre en el kardex</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>unidad_medida</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>kg, litro, lata, caja, paquete, unidad</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Unidad de medida estándar por tipo de producto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>25 valores (Menestras, Aceite…)</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Categoría específica original del kardex</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>categoria_general</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>11 grupos de negocio</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Avícolas, Cárnicos y pescados, Menestras, Lácteos, Cereales y farináceos, Conservas, Abarrotes, Bebidas e infusiones, Snacks y dulces, Limpieza e higiene, Otros</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>origen</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Categórica</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>real / sintetico</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>real = kardex del almacén; sintetico = generado para entrenamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>es_producto</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Booleana</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>True / False</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Define si el código se muestra en la app como producto o queda solo como registro técnico</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>